--- a/config/auto_configs/2024_Hyundai_Kia_Sportage PHEV(NQ5 PHEV)_G 1.6 T-GDI GAMMA2 PHEV.xlsx
+++ b/config/auto_configs/2024_Hyundai_Kia_Sportage PHEV(NQ5 PHEV)_G 1.6 T-GDI GAMMA2 PHEV.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,12 +520,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KMA_20053</t>
+          <t>KMA_10101</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -542,12 +542,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KMA_20054</t>
+          <t>KMA_10099</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -564,7 +564,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ABS/ESP</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -586,12 +586,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KMA_10104</t>
+          <t>KMA_HK_00954</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -608,12 +608,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KMA_HK_00954</t>
+          <t>KMA_10104</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -644,6 +644,820 @@
         </is>
       </c>
       <c r="D7" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KMA_20054</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KMA_20053</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IBU-TPMS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>KMA_HK_00994</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>4WD</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KMA_HK_00995</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A/C</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KMA_HK_00996</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ADAS_P</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KMA_HK_00997</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AMP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>KMA_HK_00998</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AVN</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>KMA_HK_00999</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BIC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>KMA_10098</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BMS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>KMA_10100</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CLU</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>KMA_HK_01001</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DVRS</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>KMA_HK_01003</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>KMA_HK_00966</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>E-Shifter</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>KMA_HK_01006</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>KMA_HK_01007</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FVC</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>KMA_HK_01008</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>HCU/LDC</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>KMA_10102</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>IAU</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>KMA_HK_01010</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>IBU-BCM</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>KMA_HK_01011</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>IBU-IMM</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>KMA_HK_01012</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>IBU-SKU</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>KMA_HK_01013</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ICU</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>KMA_HK_01014</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MCU</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>KMA_10103</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MLM</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>KMA_HK_01016</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>OBC</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>KMA_HK_01017</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>OCS</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>KMA_HK_01018</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PSM</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>KMA_HK_01019</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PTG</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>KMA_HK_01020</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>RCR</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>KMA_HK_01021</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ROA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>KMA_HK_01022</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>RVMS</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>KMA_HK_01023</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SCU</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>KMA_HK_01024</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SHVU-F</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>KMA_HK_01025</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SHVU-R</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>KMA_HK_01026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T-CS</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>KMA_HK_01027</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>VESS</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>KMA_HK_01028</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>WPC</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>KMA_HK_01029</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>00</t>
         </is>
